--- a/output/pdf_financials_xlsx/HYPE.xlsx
+++ b/output/pdf_financials_xlsx/HYPE.xlsx
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.09086</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.09086</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.09086</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.09086</v>
       </c>
     </row>
     <row r="93">
@@ -3594,7 +3594,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4032,7 +4036,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.09086</v>
       </c>

--- a/output/pdf_financials_xlsx/HYPE.xlsx
+++ b/output/pdf_financials_xlsx/HYPE.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.536672</v>
+        <v>0.672525</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.127448</v>
+        <v>0.302908</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.153229</v>
+        <v>0.250192</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.139443</v>
+        <v>0.314058</v>
       </c>
     </row>
     <row r="11">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.536672</v>
+        <v>-0.672525</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.127448</v>
+        <v>-0.302908</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.153229</v>
+        <v>-0.250192</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.139443</v>
+        <v>-0.314058</v>
       </c>
     </row>
     <row r="12">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.2701</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000312</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.011702</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.212613</v>
       </c>
     </row>
     <row r="35">
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.2701</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000312</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.011702</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.212613</v>
       </c>
     </row>
     <row r="37">
@@ -1367,16 +1367,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.27445</v>
+        <v>0.00435</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.000312</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.012655</v>
+        <v>0.000953</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.295217</v>
+        <v>0.082604</v>
       </c>
     </row>
     <row r="49">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6092,20 +6092,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>-0.672525</v>
+        <v>0.672525</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.302908</v>
+        <v>0.302908</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.250192</v>
+        <v>0.250192</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>-0.314058</v>
+        <v>0.314058</v>
       </c>
     </row>
     <row r="85">

--- a/output/pdf_financials_xlsx/HYPE.xlsx
+++ b/output/pdf_financials_xlsx/HYPE.xlsx
@@ -986,7 +986,7 @@
         <v>0.001844</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.002857</v>
+        <v>0.001014</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.00748</v>
@@ -1005,7 +1005,7 @@
         <v>-0.586826</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.951269</v>
+        <v>-0.953112</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.294346</v>
@@ -6428,7 +6428,11 @@
           <t>Amortization expense (note 6) $</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
